--- a/can_canoe/oakd_송출데이터_정리.xlsx
+++ b/can_canoe/oakd_송출데이터_정리.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="① 영상 미송출" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="② 영상 송출 (추가 항목)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="읽는 법·가정" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="① 영상 미송출" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="② 영상 송출 (추가 항목)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="읽는 법·가정" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R89"/>
+  <dimension ref="A1:R74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -930,7 +930,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>모델 번호(0 yolov6n,1 yolov8n,2 traffic_light,3 traffic_light_11n,4 traffic_light_v8n)</t>
+          <t>모델 번호(0 yolov6n,1 yolov8n,2 traffic_light,3 traffic_light_11n,4 traffic_light_v8n,5 a_yolom_n)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>프레임마다, 검출 개수만큼 (최대 N개)</t>
+          <t>프레임마다 검출 개수만큼(프레임당 최대 N=8개), 200 ms 마다 한 프레임분을 묶어 송신</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>프레임마다, 검출 개수만큼 (최대 N개)</t>
+          <t>프레임마다 검출 개수만큼(프레임당 최대 N=8개), 200 ms 마다 한 프레임분을 묶어 송신</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>프레임마다, 검출 개수만큼 (최대 N개)</t>
+          <t>프레임마다 검출 개수만큼(프레임당 최대 N=8개), 200 ms 마다 한 프레임분을 묶어 송신</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>프레임마다, 검출 개수만큼 (최대 N개)</t>
+          <t>프레임마다 검출 개수만큼(프레임당 최대 N=8개), 200 ms 마다 한 프레임분을 묶어 송신</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>프레임마다, 검출 개수만큼 (최대 N개)</t>
+          <t>프레임마다 검출 개수만큼(프레임당 최대 N=8개), 200 ms 마다 한 프레임분을 묶어 송신</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>프레임마다, 검출 개수만큼 (최대 N개)</t>
+          <t>프레임마다 검출 개수만큼(프레임당 최대 N=8개), 200 ms 마다 한 프레임분을 묶어 송신</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>프레임마다, 검출 개수만큼 (최대 N개)</t>
+          <t>프레임마다 검출 개수만큼(프레임당 최대 N=8개), 200 ms 마다 한 프레임분을 묶어 송신</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>프레임마다, 검출 개수만큼 (최대 N개)</t>
+          <t>프레임마다 검출 개수만큼(프레임당 최대 N=8개), 200 ms 마다 한 프레임분을 묶어 송신</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2008,52 +2008,52 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DET_POS</t>
+          <t>FRAME_META_A</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x330</t>
+          <t>0x340</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>816</v>
+        <v>832</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SeqLo</t>
+          <t>Seq</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>프레임 번호의 아래 4비트(FRAME_STATUS.Seq 와 연결)</t>
+          <t>카메라 프레임 번호(65536 에서 돌아옴)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>uint4</t>
+          <t>uint16</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0 ~ 15</t>
+          <t>0 ~ 65535</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>검출마다</t>
+          <t>프레임마다</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>프레임마다, 검출 개수만큼 (Raw 켬)</t>
+          <t>200 ms (Raw 켬)</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2071,7 +2071,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2080,128 +2080,128 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DET_POS</t>
+          <t>FRAME_META_A</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x330</t>
+          <t>0x340</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>816</v>
+        <v>832</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Index</t>
+          <t>ExposureUs</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>검출 순번(0=신뢰도 최고)</t>
+          <t>노출 시간</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>uint4</t>
+          <t>uint20</t>
         </is>
       </c>
       <c r="G23" t="n">
+        <v>20</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>0 ~ 1.04858e+06</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>프레임마다</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>200 ms (Raw 켬)</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Raw 켬</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>50</v>
+      </c>
+      <c r="O23" t="n">
+        <v>8</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q23" t="n">
         <v>4</v>
       </c>
-      <c r="H23" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>0 ~ 15</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>검출마다</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>프레임마다, 검출 개수만큼 (Raw 켬)</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>Raw 켬</t>
-        </is>
-      </c>
-      <c r="N23" t="n">
-        <v>50</v>
-      </c>
-      <c r="O23" t="n">
-        <v>8</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DET_POS</t>
+          <t>FRAME_META_A</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x330</t>
+          <t>0x340</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>816</v>
+        <v>832</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Iso</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>객체 X 위치(카메라 기준 오른쪽 +, 깊이 지도 기반)</t>
+          <t>ISO 감도</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>int16</t>
+          <t>uint12</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>mm</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-32768 ~ 32767</t>
+          <t>0 ~ 4095</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>검출마다</t>
+          <t>프레임마다</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>프레임마다, 검출 개수만큼 (Raw 켬)</t>
+          <t>200 ms (Raw 켬)</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2216,68 +2216,68 @@
         <v>8</v>
       </c>
       <c r="P24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q24" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R24" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DET_POS</t>
+          <t>FRAME_META_A</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x330</t>
+          <t>0x340</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>816</v>
+        <v>832</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>ColorTempK</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>객체 Y 위치(아래 +)</t>
+          <t>색온도</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>int16</t>
+          <t>uint14</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H25" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>K</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-32768 ~ 32767</t>
+          <t>0 ~ 16383</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>검출마다</t>
+          <t>프레임마다</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>프레임마다, 검출 개수만큼 (Raw 켬)</t>
+          <t>200 ms (Raw 켬)</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2292,37 +2292,37 @@
         <v>8</v>
       </c>
       <c r="P25" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q25" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R25" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DET_POS</t>
+          <t>FRAME_META_B</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x330</t>
+          <t>0x341</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>816</v>
+        <v>833</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>Seq</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>객체 Z 거리(앞 +)</t>
+          <t>카메라 프레임 번호(65536 에서 돌아옴)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2336,11 +2336,7 @@
       <c r="H26" t="n">
         <v>2</v>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>mm</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>0 ~ 65535</t>
@@ -2348,12 +2344,12 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>검출마다</t>
+          <t>프레임마다</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>프레임마다, 검출 개수만큼 (Raw 켬)</t>
+          <t>200 ms (Raw 켬)</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2368,64 +2364,64 @@
         <v>8</v>
       </c>
       <c r="P26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DET_ROI</t>
+          <t>FRAME_META_B</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x331</t>
+          <t>0x341</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>817</v>
+        <v>833</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>SeqLo</t>
+          <t>LensPos</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>프레임 번호의 아래 4비트(FRAME_STATUS.Seq 와 연결)</t>
+          <t>렌즈 위치(-1=고정 초점)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>uint4</t>
+          <t>int10</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H27" t="n">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0 ~ 15</t>
+          <t>-512 ~ 511</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>검출마다</t>
+          <t>프레임마다</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>프레임마다, 검출 개수만큼 (Raw 켬)</t>
+          <t>200 ms (Raw 켬)</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2440,121 +2436,125 @@
         <v>8</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DET_ROI</t>
+          <t>FRAME_META_B</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x331</t>
+          <t>0x341</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>817</v>
+        <v>833</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Index</t>
+          <t>SourceW</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>검출 순번(0=신뢰도 최고)</t>
+          <t>센서 영상 너비</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>uint4</t>
+          <t>uint13</t>
         </is>
       </c>
       <c r="G28" t="n">
+        <v>13</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>0 ~ 8191</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>프레임마다</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>200 ms (Raw 켬)</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Raw 켬</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>50</v>
+      </c>
+      <c r="O28" t="n">
+        <v>8</v>
+      </c>
+      <c r="P28" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q28" t="n">
         <v>4</v>
       </c>
-      <c r="H28" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>0 ~ 15</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>검출마다</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>프레임마다, 검출 개수만큼 (Raw 켬)</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>Raw 켬</t>
-        </is>
-      </c>
-      <c r="N28" t="n">
-        <v>50</v>
-      </c>
-      <c r="O28" t="n">
-        <v>8</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DET_ROI</t>
+          <t>FRAME_META_B</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x331</t>
+          <t>0x341</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>817</v>
+        <v>833</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>RoiX</t>
+          <t>SourceH</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>깊이 ROI 시작 X</t>
+          <t>센서 영상 높이</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>uint12</t>
+          <t>uint13</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H29" t="n">
-        <v>1.5</v>
+        <v>1.625</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2563,17 +2563,17 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0 ~ 4095</t>
+          <t>0 ~ 8191</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>검출마다</t>
+          <t>프레임마다</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>프레임마다, 검출 개수만큼 (Raw 켬)</t>
+          <t>200 ms (Raw 켬)</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2588,68 +2588,64 @@
         <v>8</v>
       </c>
       <c r="P29" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q29" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R29" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DET_ROI</t>
+          <t>FRAME_META_B</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0x331</t>
+          <t>0x341</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>817</v>
+        <v>833</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>RoiY</t>
+          <t>CamInstance</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>깊이 ROI 시작 Y</t>
+          <t>카메라 소켓 번호</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>uint12</t>
+          <t>uint4</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>px</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0 ~ 4095</t>
+          <t>0 ~ 15</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>검출마다</t>
+          <t>프레임마다</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>프레임마다, 검출 개수만큼 (Raw 켬)</t>
+          <t>200 ms (Raw 켬)</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2664,68 +2660,64 @@
         <v>8</v>
       </c>
       <c r="P30" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q30" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R30" t="n">
-        <v>20</v>
+        <v>52</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DET_ROI</t>
+          <t>FRAME_META_B</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x331</t>
+          <t>0x341</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>817</v>
+        <v>833</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>RoiW</t>
+          <t>FrameType</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>깊이 ROI 너비</t>
+          <t>영상 픽셀 형식 코드(ImgFrame type)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>uint12</t>
+          <t>uint8</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>px</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0 ~ 4095</t>
+          <t>0 ~ 255</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>검출마다</t>
+          <t>프레임마다</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>프레임마다, 검출 개수만큼 (Raw 켬)</t>
+          <t>200 ms (Raw 켬)</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2740,68 +2732,64 @@
         <v>8</v>
       </c>
       <c r="P31" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q31" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R31" t="n">
-        <v>32</v>
+        <v>56</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DET_ROI</t>
+          <t>FRAME_META_C</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x331</t>
+          <t>0x342</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>817</v>
+        <v>834</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>RoiH</t>
+          <t>Seq</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>깊이 ROI 높이</t>
+          <t>카메라 프레임 번호(65536 에서 돌아옴)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>uint12</t>
+          <t>uint16</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>px</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0 ~ 4095</t>
+          <t>0 ~ 65535</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>검출마다</t>
+          <t>프레임마다</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>프레임마다, 검출 개수만큼 (Raw 켬)</t>
+          <t>200 ms (Raw 켬)</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2816,130 +2804,134 @@
         <v>8</v>
       </c>
       <c r="P32" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FRAME_META_A</t>
+          <t>FRAME_META_C</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x340</t>
+          <t>0x342</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Seq</t>
+          <t>FrameW</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>카메라 프레임 번호(65536 에서 돌아옴)</t>
+          <t>신경망이 처리한 영상 너비</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>uint16</t>
+          <t>uint13</t>
         </is>
       </c>
       <c r="G33" t="n">
+        <v>13</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>0 ~ 8191</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>프레임마다</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>200 ms (Raw 켬)</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Raw 켬</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>50</v>
+      </c>
+      <c r="O33" t="n">
+        <v>8</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>3</v>
+      </c>
+      <c r="R33" t="n">
         <v>16</v>
-      </c>
-      <c r="H33" t="n">
-        <v>2</v>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>0 ~ 65535</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>프레임마다</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>200 ms (Raw 켬)</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>Raw 켬</t>
-        </is>
-      </c>
-      <c r="N33" t="n">
-        <v>50</v>
-      </c>
-      <c r="O33" t="n">
-        <v>8</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>FRAME_META_A</t>
+          <t>FRAME_META_C</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x340</t>
+          <t>0x342</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ExposureUs</t>
+          <t>FrameH</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>노출 시간</t>
+          <t>신경망이 처리한 영상 높이</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>uint20</t>
+          <t>uint13</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="H34" t="n">
-        <v>2.5</v>
+        <v>1.625</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>us</t>
+          <t>px</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0 ~ 1.04858e+06</t>
+          <t>0 ~ 8191</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2964,54 +2956,58 @@
         <v>8</v>
       </c>
       <c r="P34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R34" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>FRAME_META_A</t>
+          <t>FRAME_META_C</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0x340</t>
+          <t>0x342</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Iso</t>
+          <t>HfovDeg</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ISO 감도</t>
+          <t>수평 화각</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>uint12</t>
+          <t>uint11 → 실수 (×0.1)</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H35" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I35" t="inlineStr"/>
+        <v>1.375</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0 ~ 4095</t>
+          <t>0 ~ 204.7</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3036,58 +3032,58 @@
         <v>8</v>
       </c>
       <c r="P35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R35" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>FRAME_META_A</t>
+          <t>FRAME_META_C</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0x340</t>
+          <t>0x342</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ColorTempK</t>
+          <t>VfovDeg</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>색온도</t>
+          <t>수직 화각</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>uint14</t>
+          <t>uint11 → 실수 (×0.1)</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H36" t="n">
-        <v>1.75</v>
+        <v>1.375</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>deg</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0 ~ 16383</t>
+          <t>0 ~ 204.7</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3118,22 +3114,22 @@
         <v>7</v>
       </c>
       <c r="R36" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>FRAME_META_B</t>
+          <t>FRAME_TIME_DEV</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0x341</t>
+          <t>0x343</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3196,42 +3192,46 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>FRAME_META_B</t>
+          <t>FRAME_TIME_DEV</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0x341</t>
+          <t>0x343</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LensPos</t>
+          <t>TsDeviceUs</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>렌즈 위치(-1=고정 초점)</t>
+          <t>촬영 시각(카메라 시계, μs, 71.6분마다 돌아옴)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>int10</t>
+          <t>uint32</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="H38" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="I38" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>-512 ~ 511</t>
+          <t>0 ~ 4.29497e+09</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3259,7 +3259,7 @@
         <v>2</v>
       </c>
       <c r="Q38" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R38" t="n">
         <v>16</v>
@@ -3268,46 +3268,46 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>FRAME_META_B</t>
+          <t>FRAME_TIME_DEV</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x341</t>
+          <t>0x343</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SourceW</t>
+          <t>DetLatencyMs</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>센서 영상 너비</t>
+          <t>촬영→검출까지 지연</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>uint13</t>
+          <t>uint16 → 실수 (×0.1)</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H39" t="n">
-        <v>1.625</v>
+        <v>2</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>px</t>
+          <t>ms</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0 ~ 8191</t>
+          <t>0 ~ 6553.5</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3332,58 +3332,54 @@
         <v>8</v>
       </c>
       <c r="P39" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q39" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R39" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>FRAME_META_B</t>
+          <t>FRAME_TIME_HOST</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0x341</t>
+          <t>0x344</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>SourceH</t>
+          <t>Seq</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>센서 영상 높이</t>
+          <t>카메라 프레임 번호(65536 에서 돌아옴)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>uint13</t>
+          <t>uint16</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H40" t="n">
-        <v>1.625</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>px</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0 ~ 8191</t>
+          <t>0 ~ 65535</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3408,54 +3404,58 @@
         <v>8</v>
       </c>
       <c r="P40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R40" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FRAME_META_B</t>
+          <t>FRAME_TIME_HOST</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0x341</t>
+          <t>0x344</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>CamInstance</t>
+          <t>TsHostUs</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>카메라 소켓 번호</t>
+          <t>촬영 시각(호스트 시계로 동기, μs)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>uint4</t>
+          <t>uint32</t>
         </is>
       </c>
       <c r="G41" t="n">
+        <v>32</v>
+      </c>
+      <c r="H41" t="n">
         <v>4</v>
       </c>
-      <c r="H41" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0 ~ 15</t>
+          <t>0 ~ 4.29497e+09</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3480,54 +3480,58 @@
         <v>8</v>
       </c>
       <c r="P41" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Q41" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R41" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>FRAME_META_B</t>
+          <t>FRAME_TIME_HOST</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0x341</t>
+          <t>0x344</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>FrameType</t>
+          <t>FrameLatencyMs</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>영상 픽셀 형식 코드(ImgFrame type)</t>
+          <t>촬영→프레임 수신까지 지연</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>uint8</t>
+          <t>uint16 → 실수 (×0.1)</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
-      </c>
-      <c r="I42" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>ms</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0 ~ 255</t>
+          <t>0 ~ 6553.5</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3552,64 +3556,68 @@
         <v>8</v>
       </c>
       <c r="P42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q42" t="n">
         <v>7</v>
       </c>
       <c r="R42" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FRAME_META_C</t>
+          <t>DEV_TEMP</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0x342</t>
+          <t>0x350</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>834</v>
+        <v>848</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Seq</t>
+          <t>TempCss</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>카메라 프레임 번호(65536 에서 돌아옴)</t>
+          <t>칩 온도 CSS</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>uint16</t>
+          <t>uint8 → 실수 (×0.5-40)</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H43" t="n">
-        <v>2</v>
-      </c>
-      <c r="I43" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>degC</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0 ~ 65535</t>
+          <t>-40 ~ 87.5</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>프레임마다</t>
+          <t>1초</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>200 ms (Raw 켬)</t>
+          <t>1000 ms (Raw 켬)</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3627,7 +3635,7 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -3636,56 +3644,56 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>FRAME_META_C</t>
+          <t>DEV_TEMP</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0x342</t>
+          <t>0x350</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>834</v>
+        <v>848</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>FrameW</t>
+          <t>TempMss</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>신경망이 처리한 영상 너비</t>
+          <t>칩 온도 MSS</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>uint13</t>
+          <t>uint8 → 실수 (×0.5-40)</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H44" t="n">
-        <v>1.625</v>
+        <v>1</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>px</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0 ~ 8191</t>
+          <t>-40 ~ 87.5</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>프레임마다</t>
+          <t>1초</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>200 ms (Raw 켬)</t>
+          <t>1000 ms (Raw 켬)</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3700,68 +3708,68 @@
         <v>8</v>
       </c>
       <c r="P44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R44" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>FRAME_META_C</t>
+          <t>DEV_TEMP</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0x342</t>
+          <t>0x350</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>834</v>
+        <v>848</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>FrameH</t>
+          <t>TempUpa</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>신경망이 처리한 영상 높이</t>
+          <t>칩 온도 UPA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>uint13</t>
+          <t>uint8 → 실수 (×0.5-40)</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H45" t="n">
-        <v>1.625</v>
+        <v>1</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>px</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0 ~ 8191</t>
+          <t>-40 ~ 87.5</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>프레임마다</t>
+          <t>1초</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>200 ms (Raw 켬)</t>
+          <t>1000 ms (Raw 켬)</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3776,68 +3784,68 @@
         <v>8</v>
       </c>
       <c r="P45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q45" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R45" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>FRAME_META_C</t>
+          <t>DEV_TEMP</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0x342</t>
+          <t>0x350</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>834</v>
+        <v>848</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>HfovDeg</t>
+          <t>TempDss</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>수평 화각</t>
+          <t>칩 온도 DSS</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>uint11 → 실수 (×0.1)</t>
+          <t>uint8 → 실수 (×0.5-40)</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H46" t="n">
-        <v>1.375</v>
+        <v>1</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>deg</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0 ~ 204.7</t>
+          <t>-40 ~ 87.5</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>프레임마다</t>
+          <t>1초</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>200 ms (Raw 켬)</t>
+          <t>1000 ms (Raw 켬)</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3852,68 +3860,68 @@
         <v>8</v>
       </c>
       <c r="P46" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q46" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R46" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>FRAME_META_C</t>
+          <t>DEV_TEMP</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0x342</t>
+          <t>0x350</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>834</v>
+        <v>848</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VfovDeg</t>
+          <t>TempAvg</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>수직 화각</t>
+          <t>칩 평균 온도</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>uint11 → 실수 (×0.1)</t>
+          <t>uint8 → 실수 (×0.5-40)</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H47" t="n">
-        <v>1.375</v>
+        <v>1</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>deg</t>
+          <t>degC</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0 ~ 204.7</t>
+          <t>-40 ~ 87.5</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>프레임마다</t>
+          <t>1초</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>200 ms (Raw 켬)</t>
+          <t>1000 ms (Raw 켬)</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3928,64 +3936,68 @@
         <v>8</v>
       </c>
       <c r="P47" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q47" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R47" t="n">
-        <v>53</v>
+        <v>32</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FRAME_TIME_DEV</t>
+          <t>DEV_TEMP</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0x343</t>
+          <t>0x350</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>835</v>
+        <v>848</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Seq</t>
+          <t>CpuCssPct</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>카메라 프레임 번호(65536 에서 돌아옴)</t>
+          <t>LEON CSS CPU 사용률</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>uint16</t>
+          <t>uint8 → 실수 (×0.5)</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H48" t="n">
-        <v>2</v>
-      </c>
-      <c r="I48" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0 ~ 65535</t>
+          <t>0 ~ 127.5</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>프레임마다</t>
+          <t>1초</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>200 ms (Raw 켬)</t>
+          <t>1000 ms (Raw 켬)</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4000,68 +4012,68 @@
         <v>8</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q48" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>FRAME_TIME_DEV</t>
+          <t>DEV_TEMP</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0x343</t>
+          <t>0x350</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>835</v>
+        <v>848</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>TsDeviceUs</t>
+          <t>CpuMssPct</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>촬영 시각(카메라 시계, μs, 71.6분마다 돌아옴)</t>
+          <t>LEON MSS CPU 사용률</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>uint32</t>
+          <t>uint8 → 실수 (×0.5)</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="H49" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>us</t>
+          <t>%</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0 ~ 4.29497e+09</t>
+          <t>0 ~ 127.5</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>프레임마다</t>
+          <t>1초</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>200 ms (Raw 켬)</t>
+          <t>1000 ms (Raw 켬)</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4076,37 +4088,37 @@
         <v>8</v>
       </c>
       <c r="P49" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q49" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R49" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>FRAME_TIME_DEV</t>
+          <t>DEV_MEM_A</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0x343</t>
+          <t>0x351</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>835</v>
+        <v>849</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>DetLatencyMs</t>
+          <t>DdrUsedMB</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>촬영→검출까지 지연</t>
+          <t>DDR 메모리 사용량</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -4122,7 +4134,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>ms</t>
+          <t>MB</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -4132,12 +4144,12 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>프레임마다</t>
+          <t>1초</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>200 ms (Raw 켬)</t>
+          <t>1000 ms (Raw 켬)</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4152,42 +4164,42 @@
         <v>8</v>
       </c>
       <c r="P50" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="R50" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>FRAME_TIME_HOST</t>
+          <t>DEV_MEM_A</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0x344</t>
+          <t>0x351</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>836</v>
+        <v>849</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Seq</t>
+          <t>DdrTotalMB</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>카메라 프레임 번호(65536 에서 돌아옴)</t>
+          <t>DDR 메모리 전체</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>uint16</t>
+          <t>uint16 → 실수 (×0.1)</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -4196,20 +4208,24 @@
       <c r="H51" t="n">
         <v>2</v>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0 ~ 65535</t>
+          <t>0 ~ 6553.5</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>프레임마다</t>
+          <t>1초</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>200 ms (Raw 켬)</t>
+          <t>1000 ms (Raw 켬)</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4224,113 +4240,113 @@
         <v>8</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>FRAME_TIME_HOST</t>
+          <t>DEV_MEM_A</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0x344</t>
+          <t>0x351</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>836</v>
+        <v>849</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>TsHostUs</t>
+          <t>CmxUsedKB</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>촬영 시각(호스트 시계로 동기, μs)</t>
+          <t>CMX 메모리 사용량</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>uint32</t>
+          <t>uint16 → 실수 (×0.1)</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="H52" t="n">
+        <v>2</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>KB</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0 ~ 6553.5</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>1초</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>1000 ms (Raw 켬)</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Raw 켬</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>50</v>
+      </c>
+      <c r="O52" t="n">
+        <v>8</v>
+      </c>
+      <c r="P52" t="n">
         <v>4</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>us</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>0 ~ 4.29497e+09</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>프레임마다</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>200 ms (Raw 켬)</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>Raw 켬</t>
-        </is>
-      </c>
-      <c r="N52" t="n">
-        <v>50</v>
-      </c>
-      <c r="O52" t="n">
-        <v>8</v>
-      </c>
-      <c r="P52" t="n">
-        <v>2</v>
       </c>
       <c r="Q52" t="n">
         <v>5</v>
       </c>
       <c r="R52" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FRAME_TIME_HOST</t>
+          <t>DEV_MEM_A</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0x344</t>
+          <t>0x351</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>836</v>
+        <v>849</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>FrameLatencyMs</t>
+          <t>CmxTotalKB</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>촬영→프레임 수신까지 지연</t>
+          <t>CMX 메모리 전체</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -4346,7 +4362,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>ms</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -4356,12 +4372,12 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>프레임마다</t>
+          <t>1초</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>200 ms (Raw 켬)</t>
+          <t>1000 ms (Raw 켬)</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -4388,46 +4404,46 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DEV_TEMP</t>
+          <t>DEV_MEM_B</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0x350</t>
+          <t>0x352</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>TempCss</t>
+          <t>CssHeapUsedKB</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>칩 온도 CSS</t>
+          <t>LEON CSS 힙 사용량</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>uint8 → 실수 (×0.5-40)</t>
+          <t>uint32</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>degC</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>-40 ~ 87.5</t>
+          <t>0 ~ 4.29497e+09</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -4455,7 +4471,7 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
@@ -4464,46 +4480,46 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DEV_TEMP</t>
+          <t>DEV_MEM_B</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0x350</t>
+          <t>0x352</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>TempMss</t>
+          <t>CssHeapTotalKB</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>칩 온도 MSS</t>
+          <t>LEON CSS 힙 전체</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>uint8 → 실수 (×0.5-40)</t>
+          <t>uint32</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="H55" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>degC</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>-40 ~ 87.5</t>
+          <t>0 ~ 4.29497e+09</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -4528,58 +4544,58 @@
         <v>8</v>
       </c>
       <c r="P55" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q55" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R55" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DEV_TEMP</t>
+          <t>DEV_MEM_C</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0x350</t>
+          <t>0x353</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>TempUpa</t>
+          <t>MssHeapUsedKB</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>칩 온도 UPA</t>
+          <t>LEON MSS 힙 사용량</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>uint8 → 실수 (×0.5-40)</t>
+          <t>uint32</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="H56" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>degC</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>-40 ~ 87.5</t>
+          <t>0 ~ 4.29497e+09</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -4604,58 +4620,58 @@
         <v>8</v>
       </c>
       <c r="P56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R56" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DEV_TEMP</t>
+          <t>DEV_MEM_C</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0x350</t>
+          <t>0x353</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>TempDss</t>
+          <t>MssHeapTotalKB</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>칩 온도 DSS</t>
+          <t>LEON MSS 힙 전체</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>uint8 → 실수 (×0.5-40)</t>
+          <t>uint32</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="H57" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>degC</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>-40 ~ 87.5</t>
+          <t>0 ~ 4.29497e+09</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -4680,144 +4696,144 @@
         <v>8</v>
       </c>
       <c r="P57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q57" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R57" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DEV_TEMP</t>
+          <t>CALIB_A</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0x350</t>
+          <t>0x360</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>848</v>
+        <v>864</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>TempAvg</t>
+          <t>Fx</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>칩 평균 온도</t>
+          <t>초점거리 fx(픽셀)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>uint8 → 실수 (×0.5-40)</t>
+          <t>uint16 → 실수 (×0.1)</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H58" t="n">
+        <v>2</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>0 ~ 6553.5</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>10초</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>10000 ms (Raw 켬)</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Raw 켬</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>50</v>
+      </c>
+      <c r="O58" t="n">
+        <v>8</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
         <v>1</v>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>degC</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>-40 ~ 87.5</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>1초</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>1000 ms (Raw 켬)</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>Raw 켬</t>
-        </is>
-      </c>
-      <c r="N58" t="n">
-        <v>50</v>
-      </c>
-      <c r="O58" t="n">
-        <v>8</v>
-      </c>
-      <c r="P58" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>4</v>
-      </c>
       <c r="R58" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DEV_TEMP</t>
+          <t>CALIB_A</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0x350</t>
+          <t>0x360</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>848</v>
+        <v>864</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>CpuCssPct</t>
+          <t>Fy</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>LEON CSS CPU 사용률</t>
+          <t>초점거리 fy(픽셀)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>uint8 → 실수 (×0.5)</t>
+          <t>uint16 → 실수 (×0.1)</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>px</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>0 ~ 127.5</t>
+          <t>0 ~ 6553.5</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>1초</t>
+          <t>10초</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>1000 ms (Raw 켬)</t>
+          <t>10000 ms (Raw 켬)</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -4832,68 +4848,68 @@
         <v>8</v>
       </c>
       <c r="P59" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q59" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R59" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DEV_TEMP</t>
+          <t>CALIB_A</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0x350</t>
+          <t>0x360</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>848</v>
+        <v>864</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>CpuMssPct</t>
+          <t>Cx</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>LEON MSS CPU 사용률</t>
+          <t>주점 cx(픽셀, 신경망 입력 크기 기준)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>uint8 → 실수 (×0.5)</t>
+          <t>uint16 → 실수 (×0.1)</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>px</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>0 ~ 127.5</t>
+          <t>0 ~ 6553.5</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>1초</t>
+          <t>10초</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>1000 ms (Raw 켬)</t>
+          <t>10000 ms (Raw 켬)</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -4908,37 +4924,37 @@
         <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q60" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R60" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>DEV_MEM_A</t>
+          <t>CALIB_A</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0x351</t>
+          <t>0x360</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>849</v>
+        <v>864</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>DdrUsedMB</t>
+          <t>Cy</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>DDR 메모리 사용량</t>
+          <t>주점 cy(픽셀, 신경망 입력 크기 기준)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4954,7 +4970,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>MB</t>
+          <t>px</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4964,12 +4980,12 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>1초</t>
+          <t>10초</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>1000 ms (Raw 켬)</t>
+          <t>10000 ms (Raw 켬)</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -4984,68 +5000,64 @@
         <v>8</v>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q61" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DEV_MEM_A</t>
+          <t>CALIB_B</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0x351</t>
+          <t>0x361</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>849</v>
+        <v>865</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>DdrTotalMB</t>
+          <t>NClasses</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>DDR 메모리 전체</t>
+          <t>클래스 수</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>uint16 → 실수 (×0.1)</t>
+          <t>uint8</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H62" t="n">
-        <v>2</v>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>MB</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
-          <t>0 ~ 6553.5</t>
+          <t>0 ~ 255</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>1초</t>
+          <t>10초</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>1000 ms (Raw 켬)</t>
+          <t>10000 ms (Raw 켬)</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -5060,68 +5072,68 @@
         <v>8</v>
       </c>
       <c r="P62" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q62" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R62" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>DEV_MEM_A</t>
+          <t>CALIB_B</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0x351</t>
+          <t>0x361</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>849</v>
+        <v>865</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>CmxUsedKB</t>
+          <t>ConfThresholdPct</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>CMX 메모리 사용량</t>
+          <t>신뢰도 문턱값</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>uint16 → 실수 (×0.1)</t>
+          <t>uint8</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>%</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>0 ~ 6553.5</t>
+          <t>0 ~ 255</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>1초</t>
+          <t>10초</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>1000 ms (Raw 켬)</t>
+          <t>10000 ms (Raw 켬)</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -5136,42 +5148,42 @@
         <v>8</v>
       </c>
       <c r="P63" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q63" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R63" t="n">
-        <v>32</v>
+        <v>56</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DEV_MEM_A</t>
+          <t>CALIB_C</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0x351</t>
+          <t>0x362</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>849</v>
+        <v>866</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>CmxTotalKB</t>
+          <t>NnInputW</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>CMX 메모리 전체</t>
+          <t>신경망 입력 너비</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>uint16 → 실수 (×0.1)</t>
+          <t>uint16</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -5182,22 +5194,22 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>px</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>0 ~ 6553.5</t>
+          <t>0 ~ 65535</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>1초</t>
+          <t>10초</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>1000 ms (Raw 켬)</t>
+          <t>10000 ms (Raw 켬)</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5212,68 +5224,68 @@
         <v>8</v>
       </c>
       <c r="P64" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="R64" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DEV_MEM_B</t>
+          <t>CALIB_C</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0x352</t>
+          <t>0x362</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>850</v>
+        <v>866</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>CssHeapUsedKB</t>
+          <t>NnInputH</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>LEON CSS 힙 사용량</t>
+          <t>신경망 입력 높이</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>uint32</t>
+          <t>uint16</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="H65" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>px</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>0 ~ 4.29497e+09</t>
+          <t>0 ~ 65535</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>1초</t>
+          <t>10초</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>1000 ms (Raw 켬)</t>
+          <t>10000 ms (Raw 켬)</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5288,68 +5300,64 @@
         <v>8</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q65" t="n">
         <v>3</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>DEV_MEM_B</t>
+          <t>CALIB_C</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0x352</t>
+          <t>0x362</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>850</v>
+        <v>866</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>CssHeapTotalKB</t>
+          <t>CameraMask</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>LEON CSS 힙 전체</t>
+          <t>연결된 카메라 소켓 비트마스크(bit0=CAM_A)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>uint32</t>
+          <t>uint8</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="H66" t="n">
-        <v>4</v>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>KB</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
-          <t>0 ~ 4.29497e+09</t>
+          <t>0 ~ 255</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>1초</t>
+          <t>10초</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>1000 ms (Raw 켬)</t>
+          <t>10000 ms (Raw 켬)</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -5367,65 +5375,61 @@
         <v>4</v>
       </c>
       <c r="Q66" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R66" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>DEV_MEM_C</t>
+          <t>DEV_INFO</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0x353</t>
+          <t>0x370</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>851</v>
+        <v>880</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>MssHeapUsedKB</t>
+          <t>StrId</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>LEON MSS 힙 사용량</t>
+          <t>문자열 종류(0 장치ID,1 제품명,2 플랫폼,3 부트로더,4 depthai 버전,5 모델)</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>uint32</t>
+          <t>uint4</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="H67" t="n">
-        <v>4</v>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>KB</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
-          <t>0 ~ 4.29497e+09</t>
+          <t>0 ~ 15</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>1초</t>
+          <t>10초</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>1000 ms (Raw 켬)</t>
+          <t>10000 ms (Raw 켬, 문자열 5글자씩 나눠 전송)</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -5443,7 +5447,7 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
         <v>0</v>
@@ -5452,122 +5456,114 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>DEV_MEM_C</t>
+          <t>DEV_INFO</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0x353</t>
+          <t>0x370</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>851</v>
+        <v>880</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>MssHeapTotalKB</t>
+          <t>Chunk</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>LEON MSS 힙 전체</t>
+          <t>문자열 조각 번호(k번째=글자 5k~5k+4)</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>uint32</t>
+          <t>uint4</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="H68" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>0 ~ 15</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>10초</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>10000 ms (Raw 켬, 문자열 5글자씩 나눠 전송)</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Raw 켬</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>50</v>
+      </c>
+      <c r="O68" t="n">
+        <v>8</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" t="n">
         <v>4</v>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>KB</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>0 ~ 4.29497e+09</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>1초</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>1000 ms (Raw 켬)</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>Raw 켬</t>
-        </is>
-      </c>
-      <c r="N68" t="n">
-        <v>50</v>
-      </c>
-      <c r="O68" t="n">
-        <v>8</v>
-      </c>
-      <c r="P68" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>7</v>
-      </c>
-      <c r="R68" t="n">
-        <v>32</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CALIB_A</t>
+          <t>DEV_INFO</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0x360</t>
+          <t>0x370</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>864</v>
+        <v>880</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Fx</t>
+          <t>TotalLen</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>초점거리 fx(픽셀)</t>
+          <t>문자열 전체 길이</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>uint16 → 실수 (×0.1)</t>
+          <t>uint8</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H69" t="n">
-        <v>2</v>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>px</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
-          <t>0 ~ 6553.5</t>
+          <t>0 ~ 255</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -5577,7 +5573,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>10000 ms (Raw 켬)</t>
+          <t>10000 ms (Raw 켬, 문자열 5글자씩 나눠 전송)</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -5592,58 +5588,54 @@
         <v>8</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q69" t="n">
         <v>1</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CALIB_A</t>
+          <t>DEV_INFO</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0x360</t>
+          <t>0x370</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>864</v>
+        <v>880</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Fy</t>
+          <t>C0</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>초점거리 fy(픽셀)</t>
+          <t>문자열 조각의 1번째 글자(ASCII)</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>uint16 → 실수 (×0.1)</t>
+          <t>uint8</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H70" t="n">
-        <v>2</v>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>px</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
-          <t>0 ~ 6553.5</t>
+          <t>0 ~ 255</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -5653,7 +5645,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>10000 ms (Raw 켬)</t>
+          <t>10000 ms (Raw 켬, 문자열 5글자씩 나눠 전송)</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5671,7 +5663,7 @@
         <v>2</v>
       </c>
       <c r="Q70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R70" t="n">
         <v>16</v>
@@ -5680,46 +5672,42 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CALIB_A</t>
+          <t>DEV_INFO</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0x360</t>
+          <t>0x370</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>864</v>
+        <v>880</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Cx</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>주점 cx(픽셀, 신경망 입력 크기 기준)</t>
+          <t>문자열 조각의 2번째 글자(ASCII)</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>uint16 → 실수 (×0.1)</t>
+          <t>uint8</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H71" t="n">
-        <v>2</v>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>px</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
-          <t>0 ~ 6553.5</t>
+          <t>0 ~ 255</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -5729,7 +5717,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>10000 ms (Raw 켬)</t>
+          <t>10000 ms (Raw 켬, 문자열 5글자씩 나눠 전송)</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5744,58 +5732,54 @@
         <v>8</v>
       </c>
       <c r="P71" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q71" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R71" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CALIB_A</t>
+          <t>DEV_INFO</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0x360</t>
+          <t>0x370</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>864</v>
+        <v>880</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Cy</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>주점 cy(픽셀, 신경망 입력 크기 기준)</t>
+          <t>문자열 조각의 3번째 글자(ASCII)</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>uint16 → 실수 (×0.1)</t>
+          <t>uint8</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H72" t="n">
-        <v>2</v>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>px</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
-          <t>0 ~ 6553.5</t>
+          <t>0 ~ 255</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -5805,7 +5789,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>10000 ms (Raw 켬)</t>
+          <t>10000 ms (Raw 켬, 문자열 5글자씩 나눠 전송)</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -5820,58 +5804,54 @@
         <v>8</v>
       </c>
       <c r="P72" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q72" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R72" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CALIB_B</t>
+          <t>DEV_INFO</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0x361</t>
+          <t>0x370</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>865</v>
+        <v>880</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>BaselineCm</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>스테레오 기선 길이</t>
+          <t>문자열 조각의 4번째 글자(ASCII)</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>uint16 → 실수 (×0.01)</t>
+          <t>uint8</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H73" t="n">
-        <v>2</v>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>cm</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
-          <t>0 ~ 655.35</t>
+          <t>0 ~ 255</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -5881,7 +5861,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>10000 ms (Raw 켬)</t>
+          <t>10000 ms (Raw 켬, 문자열 5글자씩 나눠 전송)</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -5896,58 +5876,54 @@
         <v>8</v>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q73" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>CALIB_B</t>
+          <t>DEV_INFO</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0x361</t>
+          <t>0x370</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>865</v>
+        <v>880</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>DepthLoMm</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>유효 깊이 최소</t>
+          <t>문자열 조각의 5번째 글자(ASCII)</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>uint16</t>
+          <t>uint8</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H74" t="n">
-        <v>2</v>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>mm</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
-          <t>0 ~ 65535</t>
+          <t>0 ~ 255</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5957,7 +5933,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>10000 ms (Raw 켬)</t>
+          <t>10000 ms (Raw 켬, 문자열 5글자씩 나눠 전송)</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -5972,1108 +5948,12 @@
         <v>8</v>
       </c>
       <c r="P74" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q74" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R74" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>CALIB_B</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>0x361</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>865</v>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>DepthHiMm</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>유효 깊이 최대</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>uint16</t>
-        </is>
-      </c>
-      <c r="G75" t="n">
-        <v>16</v>
-      </c>
-      <c r="H75" t="n">
-        <v>2</v>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>0 ~ 65535</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>10초</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>10000 ms (Raw 켬)</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>Raw 켬</t>
-        </is>
-      </c>
-      <c r="N75" t="n">
-        <v>50</v>
-      </c>
-      <c r="O75" t="n">
-        <v>8</v>
-      </c>
-      <c r="P75" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>5</v>
-      </c>
-      <c r="R75" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>CALIB_B</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>0x361</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>865</v>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>NClasses</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>클래스 수</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>uint8</t>
-        </is>
-      </c>
-      <c r="G76" t="n">
-        <v>8</v>
-      </c>
-      <c r="H76" t="n">
-        <v>1</v>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>0 ~ 255</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>10초</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>10000 ms (Raw 켬)</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>Raw 켬</t>
-        </is>
-      </c>
-      <c r="N76" t="n">
-        <v>50</v>
-      </c>
-      <c r="O76" t="n">
-        <v>8</v>
-      </c>
-      <c r="P76" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>6</v>
-      </c>
-      <c r="R76" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>CALIB_B</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>0x361</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>865</v>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>ConfThresholdPct</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>신뢰도 문턱값</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>uint8</t>
-        </is>
-      </c>
-      <c r="G77" t="n">
-        <v>8</v>
-      </c>
-      <c r="H77" t="n">
-        <v>1</v>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>0 ~ 255</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>10초</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>10000 ms (Raw 켬)</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>Raw 켬</t>
-        </is>
-      </c>
-      <c r="N77" t="n">
-        <v>50</v>
-      </c>
-      <c r="O77" t="n">
-        <v>8</v>
-      </c>
-      <c r="P77" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q77" t="n">
-        <v>7</v>
-      </c>
-      <c r="R77" t="n">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>CALIB_C</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>0x362</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>866</v>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>NnInputW</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>신경망 입력 너비</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>uint16</t>
-        </is>
-      </c>
-      <c r="G78" t="n">
-        <v>16</v>
-      </c>
-      <c r="H78" t="n">
-        <v>2</v>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>px</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>0 ~ 65535</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>10초</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>10000 ms (Raw 켬)</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>Raw 켬</t>
-        </is>
-      </c>
-      <c r="N78" t="n">
-        <v>50</v>
-      </c>
-      <c r="O78" t="n">
-        <v>8</v>
-      </c>
-      <c r="P78" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>1</v>
-      </c>
-      <c r="R78" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>CALIB_C</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>0x362</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>866</v>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>NnInputH</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>신경망 입력 높이</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>uint16</t>
-        </is>
-      </c>
-      <c r="G79" t="n">
-        <v>16</v>
-      </c>
-      <c r="H79" t="n">
-        <v>2</v>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>px</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>0 ~ 65535</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>10초</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>10000 ms (Raw 켬)</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>Raw 켬</t>
-        </is>
-      </c>
-      <c r="N79" t="n">
-        <v>50</v>
-      </c>
-      <c r="O79" t="n">
-        <v>8</v>
-      </c>
-      <c r="P79" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>3</v>
-      </c>
-      <c r="R79" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>CALIB_C</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>0x362</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>866</v>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>SpatialOn</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>깊이 위치 계산 켬 여부</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>bool(1bit)</t>
-        </is>
-      </c>
-      <c r="G80" t="n">
-        <v>1</v>
-      </c>
-      <c r="H80" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>0 ~ 1</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>10초</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>10000 ms (Raw 켬)</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>Raw 켬</t>
-        </is>
-      </c>
-      <c r="N80" t="n">
-        <v>50</v>
-      </c>
-      <c r="O80" t="n">
-        <v>8</v>
-      </c>
-      <c r="P80" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>4</v>
-      </c>
-      <c r="R80" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>CALIB_C</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>0x362</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>866</v>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>CameraMask</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>연결된 카메라 소켓 비트마스크(bit0=CAM_A)</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>uint8</t>
-        </is>
-      </c>
-      <c r="G81" t="n">
-        <v>8</v>
-      </c>
-      <c r="H81" t="n">
-        <v>1</v>
-      </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>0 ~ 255</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>10초</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>10000 ms (Raw 켬)</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>Raw 켬</t>
-        </is>
-      </c>
-      <c r="N81" t="n">
-        <v>50</v>
-      </c>
-      <c r="O81" t="n">
-        <v>8</v>
-      </c>
-      <c r="P81" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>5</v>
-      </c>
-      <c r="R81" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>DEV_INFO</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>0x370</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>880</v>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>StrId</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>문자열 종류(0 장치ID,1 제품명,2 플랫폼,3 부트로더,4 depthai 버전,5 모델)</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>uint4</t>
-        </is>
-      </c>
-      <c r="G82" t="n">
-        <v>4</v>
-      </c>
-      <c r="H82" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>0 ~ 15</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>10초</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>10000 ms (Raw 켬, 문자열 5글자씩 나눠 전송)</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>Raw 켬</t>
-        </is>
-      </c>
-      <c r="N82" t="n">
-        <v>50</v>
-      </c>
-      <c r="O82" t="n">
-        <v>8</v>
-      </c>
-      <c r="P82" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
-      <c r="R82" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>DEV_INFO</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>0x370</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>880</v>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Chunk</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>문자열 조각 번호(k번째=글자 5k~5k+4)</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>uint4</t>
-        </is>
-      </c>
-      <c r="G83" t="n">
-        <v>4</v>
-      </c>
-      <c r="H83" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>0 ~ 15</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>10초</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>10000 ms (Raw 켬, 문자열 5글자씩 나눠 전송)</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>Raw 켬</t>
-        </is>
-      </c>
-      <c r="N83" t="n">
-        <v>50</v>
-      </c>
-      <c r="O83" t="n">
-        <v>8</v>
-      </c>
-      <c r="P83" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
-      <c r="R83" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>DEV_INFO</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>0x370</t>
-        </is>
-      </c>
-      <c r="C84" t="n">
-        <v>880</v>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>TotalLen</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>문자열 전체 길이</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>uint8</t>
-        </is>
-      </c>
-      <c r="G84" t="n">
-        <v>8</v>
-      </c>
-      <c r="H84" t="n">
-        <v>1</v>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>0 ~ 255</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>10초</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>10000 ms (Raw 켬, 문자열 5글자씩 나눠 전송)</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>Raw 켬</t>
-        </is>
-      </c>
-      <c r="N84" t="n">
-        <v>50</v>
-      </c>
-      <c r="O84" t="n">
-        <v>8</v>
-      </c>
-      <c r="P84" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q84" t="n">
-        <v>1</v>
-      </c>
-      <c r="R84" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>DEV_INFO</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>0x370</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
-        <v>880</v>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>C0</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>문자열 조각의 1번째 글자(ASCII)</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>uint8</t>
-        </is>
-      </c>
-      <c r="G85" t="n">
-        <v>8</v>
-      </c>
-      <c r="H85" t="n">
-        <v>1</v>
-      </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>0 ~ 255</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>10초</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>10000 ms (Raw 켬, 문자열 5글자씩 나눠 전송)</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>Raw 켬</t>
-        </is>
-      </c>
-      <c r="N85" t="n">
-        <v>50</v>
-      </c>
-      <c r="O85" t="n">
-        <v>8</v>
-      </c>
-      <c r="P85" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q85" t="n">
-        <v>2</v>
-      </c>
-      <c r="R85" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>DEV_INFO</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>0x370</t>
-        </is>
-      </c>
-      <c r="C86" t="n">
-        <v>880</v>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>문자열 조각의 2번째 글자(ASCII)</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>uint8</t>
-        </is>
-      </c>
-      <c r="G86" t="n">
-        <v>8</v>
-      </c>
-      <c r="H86" t="n">
-        <v>1</v>
-      </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>0 ~ 255</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>10초</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>10000 ms (Raw 켬, 문자열 5글자씩 나눠 전송)</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>Raw 켬</t>
-        </is>
-      </c>
-      <c r="N86" t="n">
-        <v>50</v>
-      </c>
-      <c r="O86" t="n">
-        <v>8</v>
-      </c>
-      <c r="P86" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q86" t="n">
-        <v>3</v>
-      </c>
-      <c r="R86" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>DEV_INFO</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>0x370</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
-        <v>880</v>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>문자열 조각의 3번째 글자(ASCII)</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>uint8</t>
-        </is>
-      </c>
-      <c r="G87" t="n">
-        <v>8</v>
-      </c>
-      <c r="H87" t="n">
-        <v>1</v>
-      </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>0 ~ 255</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>10초</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>10000 ms (Raw 켬, 문자열 5글자씩 나눠 전송)</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>Raw 켬</t>
-        </is>
-      </c>
-      <c r="N87" t="n">
-        <v>50</v>
-      </c>
-      <c r="O87" t="n">
-        <v>8</v>
-      </c>
-      <c r="P87" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q87" t="n">
-        <v>4</v>
-      </c>
-      <c r="R87" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>DEV_INFO</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>0x370</t>
-        </is>
-      </c>
-      <c r="C88" t="n">
-        <v>880</v>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>문자열 조각의 4번째 글자(ASCII)</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>uint8</t>
-        </is>
-      </c>
-      <c r="G88" t="n">
-        <v>8</v>
-      </c>
-      <c r="H88" t="n">
-        <v>1</v>
-      </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>0 ~ 255</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>10초</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>10000 ms (Raw 켬, 문자열 5글자씩 나눠 전송)</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>Raw 켬</t>
-        </is>
-      </c>
-      <c r="N88" t="n">
-        <v>50</v>
-      </c>
-      <c r="O88" t="n">
-        <v>8</v>
-      </c>
-      <c r="P88" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q88" t="n">
-        <v>5</v>
-      </c>
-      <c r="R88" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>DEV_INFO</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>0x370</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
-        <v>880</v>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>문자열 조각의 5번째 글자(ASCII)</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>uint8</t>
-        </is>
-      </c>
-      <c r="G89" t="n">
-        <v>8</v>
-      </c>
-      <c r="H89" t="n">
-        <v>1</v>
-      </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>0 ~ 255</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>10초</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>10000 ms (Raw 켬, 문자열 5글자씩 나눠 전송)</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>Raw 켬</t>
-        </is>
-      </c>
-      <c r="N89" t="n">
-        <v>50</v>
-      </c>
-      <c r="O89" t="n">
-        <v>8</v>
-      </c>
-      <c r="P89" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q89" t="n">
-        <v>6</v>
-      </c>
-      <c r="R89" t="n">
         <v>48</v>
       </c>
     </row>
@@ -7176,7 +6056,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>신경망 입력과 같은 크기의 컬러 영상. 모델마다 다름</t>
+          <t>신경망 입력과 같은 크기의 컬러 영상 (A-YOLOM(n) 512×288)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -7186,11 +6066,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>traffic_light 416×416</t>
+          <t>512×288</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>519168</v>
+        <v>442368</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -7198,16 +6078,16 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>20.76672</v>
+        <v>17.69472</v>
       </c>
       <c r="H4" t="n">
-        <v>64896</v>
+        <v>55296</v>
       </c>
       <c r="I4" t="n">
-        <v>17.5</v>
+        <v>14.9</v>
       </c>
       <c r="J4" t="n">
-        <v>8112</v>
+        <v>6912</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -7218,17 +6098,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RGB 프레임(yolov6n 입력)</t>
+          <t>1채널 영상 또는 마스크</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>yolov6n 입력 크기</t>
+          <t>512×288 1채널(흑백 영상·마스크 한 장)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>uint8 × (W×H×3)</t>
+          <t>uint8 × (W×H)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -7237,7 +6117,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>442368</v>
+        <v>147456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -7245,16 +6125,16 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>17.69472</v>
+        <v>5.89824</v>
       </c>
       <c r="H5" t="n">
-        <v>55296</v>
+        <v>18432</v>
       </c>
       <c r="I5" t="n">
-        <v>14.9</v>
+        <v>5</v>
       </c>
       <c r="J5" t="n">
-        <v>6912</v>
+        <v>2304</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -7265,26 +6145,26 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>깊이 프레임(depth)</t>
+          <t>신경망 원시 출력(마스크 logit 포함)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>스테레오 깊이 지도(밀리미터). 640×400 가정 — 실측으로 확인</t>
+          <t>det_p3/p4/p5 + 분할 logit. 모든 조건에서 이더넷으로 옴 (호스트 디코딩에 필요). FP16 가정</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>uint16 × (W×H)</t>
+          <t>FP16 × (69×(36·64+18·32+9·16) + 2×2·288·512)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>640×400 (가정)</t>
+          <t>원본 ft1</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>512000</v>
+        <v>1007136</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -7292,16 +6172,16 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>20.48</v>
+        <v>40.28544</v>
       </c>
       <c r="H6" t="n">
-        <v>64000</v>
+        <v>125892</v>
       </c>
       <c r="I6" t="n">
-        <v>17.3</v>
+        <v>34</v>
       </c>
       <c r="J6" t="n">
-        <v>8000</v>
+        <v>15737</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -7350,7 +6230,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CANdb 송신 주기 50 ms: 교수님 요청 열. 카메라 값은 5 fps(=200 ms)마다 갱신되므로 50 ms 로 보내면 4번 중 1번만 새 값이다.</t>
+          <t>CANdb 수신 주기 50 ms: 교수님 요청 열(수신 노드가 이 간격으로 값을 읽는다는 기준). 실제 송신은 5 fps(=200 ms) 프레임 단위·1초·10초 이벤트 송신이며 50 ms 반복 송신이 아니다 → 수신을 50 ms 로 읽으면 4번 중 1번만 새 값. DBC 의 GenMsgCycleTime 은 PERF=1000 만 값이 있고 나머지는 0(이벤트)이라 이 열과 다르다.</t>
         </is>
       </c>
     </row>
@@ -7378,7 +6258,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>변수 88개 / 메시지 18개 (DBC 에서 자동 생성)</t>
+          <t>변수 73개 / 메시지 16개 (DBC 에서 자동 생성, 깊이 관련·차선 요약 제외: DET_POS, DET_ROI, SEG_SUMMARY 전체와 CALIB_B 의 BaselineCm·DepthLoMm·DepthHiMm, CALIB_C 의 SpatialOn)</t>
         </is>
       </c>
     </row>
